--- a/data/industry_cache/20261025/industry_observation.xlsx
+++ b/data/industry_cache/20261025/industry_observation.xlsx
@@ -555,22 +555,22 @@
         <v>87.02</v>
       </c>
       <c r="H2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
         <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.16</v>
+        <v>-1.13</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.21</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.62</v>
+        <v>-15.62</v>
       </c>
       <c r="N2" t="n">
         <v>-0.4</v>
@@ -629,22 +629,22 @@
         <v>51.2</v>
       </c>
       <c r="H3" t="n">
-        <v>6.41</v>
+        <v>5.58</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J3" t="n">
-        <v>2.37</v>
+        <v>1.54</v>
       </c>
       <c r="K3" t="n">
-        <v>14.76</v>
+        <v>14.14</v>
       </c>
       <c r="L3" t="n">
         <v>83.33</v>
       </c>
       <c r="M3" t="n">
-        <v>7.85</v>
+        <v>7.23</v>
       </c>
       <c r="N3" t="n">
         <v>-1.74</v>
@@ -786,13 +786,13 @@
         <v>4.78</v>
       </c>
       <c r="K5" t="n">
-        <v>22.08</v>
+        <v>21.34</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>9.699999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>-2.25</v>
@@ -851,22 +851,22 @@
         <v>67.91</v>
       </c>
       <c r="H6" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="K6" t="n">
-        <v>12.45</v>
+        <v>15.43</v>
       </c>
       <c r="L6" t="n">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>4.63</v>
+        <v>7.61</v>
       </c>
       <c r="N6" t="n">
         <v>0.15</v>
@@ -934,13 +934,13 @@
         <v>-0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>13.15</v>
+        <v>11.67</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>4.72</v>
       </c>
       <c r="N7" t="n">
         <v>1.51</v>
@@ -999,22 +999,22 @@
         <v>54.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.18</v>
+        <v>-2.74</v>
       </c>
       <c r="K8" t="n">
-        <v>5.09</v>
+        <v>5.38</v>
       </c>
       <c r="L8" t="n">
         <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.94</v>
+        <v>-7.66</v>
       </c>
       <c r="N8" t="n">
         <v>0.44</v>
@@ -1073,22 +1073,22 @@
         <v>62.78</v>
       </c>
       <c r="H9" t="n">
-        <v>7.18</v>
+        <v>7.44</v>
       </c>
       <c r="I9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J9" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
-        <v>8.5</v>
+        <v>8.65</v>
       </c>
       <c r="L9" t="n">
         <v>20.83</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>-0.5600000000000001</v>
@@ -1147,22 +1147,22 @@
         <v>58.2</v>
       </c>
       <c r="H10" t="n">
-        <v>8.550000000000001</v>
+        <v>5.96</v>
       </c>
       <c r="I10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J10" t="n">
-        <v>4.79</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="L10" t="n">
         <v>95.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="N10" t="n">
         <v>-1.66</v>
@@ -1230,13 +1230,13 @@
         <v>-1.74</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="L11" t="n">
-        <v>62.5</v>
+        <v>58.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="N11" t="n">
         <v>-2.43</v>
@@ -1295,22 +1295,22 @@
         <v>80.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.64</v>
+        <v>5.09</v>
       </c>
       <c r="I12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J12" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="K12" t="n">
-        <v>6.53</v>
+        <v>6.18</v>
       </c>
       <c r="L12" t="n">
         <v>37.5</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.16</v>
+        <v>-0.51</v>
       </c>
       <c r="N12" t="n">
         <v>0.75</v>
@@ -1369,22 +1369,22 @@
         <v>46.15</v>
       </c>
       <c r="H13" t="n">
-        <v>7.56</v>
+        <v>7.16</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="K13" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="L13" t="n">
         <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.07</v>
+        <v>-1.09</v>
       </c>
       <c r="N13" t="n">
         <v>-1.99</v>
@@ -1443,22 +1443,22 @@
         <v>57.89</v>
       </c>
       <c r="H14" t="n">
-        <v>3.44</v>
+        <v>4.16</v>
       </c>
       <c r="I14" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.6</v>
+        <v>-0.88</v>
       </c>
       <c r="K14" t="n">
-        <v>9.039999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>83.33</v>
+        <v>79.17</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.09</v>
+        <v>-0.28</v>
       </c>
       <c r="N14" t="n">
         <v>-2.9</v>
@@ -1517,22 +1517,22 @@
         <v>62.63</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.28</v>
+        <v>-0.22</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.77</v>
+        <v>-0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="L15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.97</v>
+        <v>4.58</v>
       </c>
       <c r="N15" t="n">
         <v>-3.61</v>
@@ -1591,22 +1591,22 @@
         <v>60.37</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J16" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="K16" t="n">
-        <v>7.53</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>5.19</v>
       </c>
       <c r="N16" t="n">
         <v>-0.9399999999999999</v>
@@ -1665,22 +1665,22 @@
         <v>24.32</v>
       </c>
       <c r="H17" t="n">
-        <v>6.01</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J17" t="n">
-        <v>0.87</v>
+        <v>0.25</v>
       </c>
       <c r="K17" t="n">
-        <v>6.32</v>
+        <v>4.76</v>
       </c>
       <c r="L17" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M17" t="n">
-        <v>0.18</v>
+        <v>-1.38</v>
       </c>
       <c r="N17" t="n">
         <v>-1.87</v>
@@ -1813,22 +1813,22 @@
         <v>26.34</v>
       </c>
       <c r="H19" t="n">
-        <v>4.54</v>
+        <v>4.76</v>
       </c>
       <c r="I19" t="n">
         <v>65</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.87</v>
+        <v>-0.65</v>
       </c>
       <c r="K19" t="n">
-        <v>11.26</v>
+        <v>10.97</v>
       </c>
       <c r="L19" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M19" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="N19" t="n">
         <v>-1.32</v>
@@ -1961,22 +1961,22 @@
         <v>67.83</v>
       </c>
       <c r="H21" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="I21" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>12.29</v>
+        <v>10.92</v>
       </c>
       <c r="L21" t="n">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="M21" t="n">
-        <v>7.68</v>
+        <v>6.31</v>
       </c>
       <c r="N21" t="n">
         <v>-2.21</v>
@@ -2035,22 +2035,22 @@
         <v>30.61</v>
       </c>
       <c r="H22" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>0.96</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>20.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0.77</v>
+        <v>-1.37</v>
       </c>
       <c r="N22" t="n">
         <v>-2.5</v>
@@ -2109,22 +2109,22 @@
         <v>52.91</v>
       </c>
       <c r="H23" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="I23" t="n">
         <v>55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="K23" t="n">
-        <v>13.77</v>
+        <v>13.51</v>
       </c>
       <c r="L23" t="n">
         <v>87.5</v>
       </c>
       <c r="M23" t="n">
-        <v>5.35</v>
+        <v>5.09</v>
       </c>
       <c r="N23" t="n">
         <v>-3.54</v>
@@ -2183,22 +2183,22 @@
         <v>47.16</v>
       </c>
       <c r="H24" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="I24" t="n">
         <v>40</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="K24" t="n">
-        <v>8.07</v>
+        <v>7.39</v>
       </c>
       <c r="L24" t="n">
-        <v>79.17</v>
+        <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="N24" t="n">
         <v>3.01</v>
@@ -2257,22 +2257,22 @@
         <v>59.36</v>
       </c>
       <c r="H25" t="n">
-        <v>2.27</v>
+        <v>0.55</v>
       </c>
       <c r="I25" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>0.42</v>
+        <v>-1.3</v>
       </c>
       <c r="K25" t="n">
-        <v>1.22</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.53</v>
+        <v>-4.29</v>
       </c>
       <c r="N25" t="n">
         <v>0.32</v>
@@ -2290,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2331,22 +2331,22 @@
         <v>31.55</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="I26" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J26" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="K26" t="n">
-        <v>7.74</v>
+        <v>7.06</v>
       </c>
       <c r="L26" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M26" t="n">
-        <v>5.83</v>
+        <v>5.15</v>
       </c>
       <c r="N26" t="n">
         <v>5.21</v>
@@ -2414,13 +2414,13 @@
         <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>10.09</v>
+        <v>-1.6</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.93</v>
+        <v>-5.76</v>
       </c>
       <c r="N27" t="n">
         <v>-0.53</v>
@@ -2479,22 +2479,22 @@
         <v>43.82</v>
       </c>
       <c r="H28" t="n">
-        <v>8.289999999999999</v>
+        <v>5.12</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J28" t="n">
-        <v>5.58</v>
+        <v>2.42</v>
       </c>
       <c r="K28" t="n">
-        <v>12.43</v>
+        <v>11.74</v>
       </c>
       <c r="L28" t="n">
         <v>70.83</v>
       </c>
       <c r="M28" t="n">
-        <v>-9.99</v>
+        <v>-10.69</v>
       </c>
       <c r="N28" t="n">
         <v>-3.6</v>
@@ -2627,22 +2627,22 @@
         <v>55.43</v>
       </c>
       <c r="H30" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="J30" t="n">
-        <v>1.82</v>
+        <v>0.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>11.58</v>
       </c>
       <c r="L30" t="n">
-        <v>29.17</v>
+        <v>95.83</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.17</v>
+        <v>6.71</v>
       </c>
       <c r="N30" t="n">
         <v>-1.54</v>
@@ -2701,22 +2701,22 @@
         <v>42.84</v>
       </c>
       <c r="H31" t="n">
-        <v>4.18</v>
+        <v>2.53</v>
       </c>
       <c r="I31" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J31" t="n">
-        <v>0.83</v>
+        <v>-0.82</v>
       </c>
       <c r="K31" t="n">
-        <v>8.56</v>
+        <v>7.76</v>
       </c>
       <c r="L31" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M31" t="n">
-        <v>6.77</v>
+        <v>5.98</v>
       </c>
       <c r="N31" t="n">
         <v>-1.76</v>
@@ -2734,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
